--- a/data/trans_orig/P6716-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6716-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2012</t>
+          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2012 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20187</t>
+          <t>19598</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46679</t>
+          <t>46986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29550</t>
+          <t>29066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51470</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60265</t>
+          <t>58749</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90067</t>
+          <t>90833</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>33159</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57833</t>
+          <t>56791</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15256</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>32593</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52251</t>
+          <t>53763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82976</t>
+          <t>81846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77790</t>
+          <t>77372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104726</t>
+          <t>105184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57873</t>
+          <t>58553</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82331</t>
+          <t>84234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144957</t>
+          <t>144553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180584</t>
+          <t>180413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,68%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34642</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29647</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32782</t>
+          <t>31180</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58700</t>
+          <t>57321</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27161</t>
+          <t>25963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50562</t>
+          <t>50566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>26031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50521</t>
+          <t>50651</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91278</t>
+          <t>92516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152008</t>
+          <t>153398</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>200145</t>
+          <t>203420</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113390</t>
+          <t>111956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153917</t>
+          <t>154081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>276341</t>
+          <t>277376</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>343419</t>
+          <t>344899</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210277</t>
+          <t>209733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265149</t>
+          <t>265017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>125440</t>
+          <t>126820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170694</t>
+          <t>169737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>349124</t>
+          <t>347293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>423448</t>
+          <t>422150</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>407703</t>
+          <t>410096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>469525</t>
+          <t>472551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>210377</t>
+          <t>211113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>257666</t>
+          <t>257052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>637838</t>
+          <t>636866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>715814</t>
+          <t>716452</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20527</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25586</t>
+          <t>25711</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24098</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58827</t>
+          <t>57859</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21415</t>
+          <t>22067</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>43517</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59608</t>
+          <t>59627</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95120</t>
+          <t>94430</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55123</t>
+          <t>56616</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86755</t>
+          <t>87394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41145</t>
+          <t>41673</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67995</t>
+          <t>69590</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102970</t>
+          <t>104377</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144219</t>
+          <t>145467</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158932</t>
+          <t>159319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197236</t>
+          <t>197227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123974</t>
+          <t>124461</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156257</t>
+          <t>155688</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>292015</t>
+          <t>295273</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>343260</t>
+          <t>343009</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27808</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52839</t>
+          <t>53528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19335</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39522</t>
+          <t>41410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51309</t>
+          <t>53014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84670</t>
+          <t>84257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44166</t>
+          <t>45212</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77022</t>
+          <t>77049</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31899</t>
+          <t>31723</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58255</t>
+          <t>59498</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83969</t>
+          <t>84527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126010</t>
+          <t>128660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>224988</t>
+          <t>227119</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>286496</t>
+          <t>288714</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>175906</t>
+          <t>181231</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>229929</t>
+          <t>232342</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>421448</t>
+          <t>421616</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>500601</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>320465</t>
+          <t>321232</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>386466</t>
+          <t>386459</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>198303</t>
+          <t>198059</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>250875</t>
+          <t>250288</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>527343</t>
+          <t>534659</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>616738</t>
+          <t>617599</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>674283</t>
+          <t>671408</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>752463</t>
+          <t>746722</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>410519</t>
+          <t>410876</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>476275</t>
+          <t>475399</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1109461</t>
+          <t>1108845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1208748</t>
+          <t>1203796</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2016</t>
+          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>15881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22943</t>
+          <t>24833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22615</t>
+          <t>22261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16290</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>14897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34718</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28786</t>
+          <t>28115</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49767</t>
+          <t>50126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24349</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41445</t>
+          <t>43806</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68487</t>
+          <t>68759</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45201</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>30391</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43663</t>
+          <t>44046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70745</t>
+          <t>69512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36424</t>
+          <t>36193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59639</t>
+          <t>58801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27420</t>
+          <t>27026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52420</t>
+          <t>53620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79831</t>
+          <t>80144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>24121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49086</t>
+          <t>49375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46429</t>
+          <t>46258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51836</t>
+          <t>53208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85340</t>
+          <t>89506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43692</t>
+          <t>42043</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74888</t>
+          <t>73866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31918</t>
+          <t>32501</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58299</t>
+          <t>58368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83879</t>
+          <t>82490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124503</t>
+          <t>123352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190529</t>
+          <t>189424</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>240879</t>
+          <t>242360</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>151392</t>
+          <t>146897</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>194984</t>
+          <t>192928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>351106</t>
+          <t>351745</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>423124</t>
+          <t>419730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>248546</t>
+          <t>249733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>301941</t>
+          <t>304424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158759</t>
+          <t>155891</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204726</t>
+          <t>202871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>414727</t>
+          <t>423608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>491984</t>
+          <t>494173</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>312019</t>
+          <t>315179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371733</t>
+          <t>373583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202673</t>
+          <t>202949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248303</t>
+          <t>246372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>530327</t>
+          <t>531479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>607153</t>
+          <t>607853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>19839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>20599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>15184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>36899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47396</t>
+          <t>47773</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79325</t>
+          <t>79045</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41482</t>
+          <t>41584</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69443</t>
+          <t>69002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99237</t>
+          <t>96342</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140215</t>
+          <t>137978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68835</t>
+          <t>67291</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101163</t>
+          <t>101372</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54957</t>
+          <t>55594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83434</t>
+          <t>82175</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131657</t>
+          <t>129806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174408</t>
+          <t>175999</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168823</t>
+          <t>169479</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206829</t>
+          <t>207333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>147365</t>
+          <t>146387</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>179952</t>
+          <t>180327</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>323923</t>
+          <t>322068</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>377021</t>
+          <t>375183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36263</t>
+          <t>35313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>66964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>36345</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62420</t>
+          <t>61989</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78368</t>
+          <t>76123</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118742</t>
+          <t>117173</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>64838</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>102981</t>
+          <t>103626</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49606</t>
+          <t>50986</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>81871</t>
+          <t>82180</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>125077</t>
+          <t>128175</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>173991</t>
+          <t>172962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>283646</t>
+          <t>284236</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>350131</t>
+          <t>349113</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>216288</t>
+          <t>213989</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>269004</t>
+          <t>269888</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>517971</t>
+          <t>518632</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>601063</t>
+          <t>605349</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>360545</t>
+          <t>361149</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>428376</t>
+          <t>427989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>243746</t>
+          <t>242165</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>298461</t>
+          <t>296516</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>620689</t>
+          <t>617771</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>708991</t>
+          <t>707492</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>540655</t>
+          <t>534810</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>617875</t>
+          <t>612805</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>372966</t>
+          <t>374819</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>437761</t>
+          <t>436617</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>933981</t>
+          <t>932968</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1032544</t>
+          <t>1034394</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6716-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6716-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>25581</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46986</t>
+          <t>48130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>28804</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58749</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90833</t>
+          <t>90862</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33159</t>
+          <t>33682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56791</t>
+          <t>56966</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14909</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53763</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81846</t>
+          <t>83323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77372</t>
+          <t>78004</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105184</t>
+          <t>105132</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58553</t>
+          <t>58112</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84234</t>
+          <t>82897</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144553</t>
+          <t>143324</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180413</t>
+          <t>179680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>30745</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31180</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57321</t>
+          <t>59263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>26802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50566</t>
+          <t>50626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>25196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50651</t>
+          <t>51041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>58800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92516</t>
+          <t>93488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>153398</t>
+          <t>153541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>203420</t>
+          <t>202978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111956</t>
+          <t>114151</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154081</t>
+          <t>155013</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>277376</t>
+          <t>277914</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>344899</t>
+          <t>340135</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>209733</t>
+          <t>208822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265017</t>
+          <t>266293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126820</t>
+          <t>127488</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169737</t>
+          <t>169469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>347293</t>
+          <t>350101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>422150</t>
+          <t>419458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>410096</t>
+          <t>409646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>472551</t>
+          <t>472149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211113</t>
+          <t>209633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>257052</t>
+          <t>257404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636866</t>
+          <t>636968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716452</t>
+          <t>711836</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,9%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25711</t>
+          <t>24352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32152</t>
+          <t>30051</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57859</t>
+          <t>56863</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>21269</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43517</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59627</t>
+          <t>59601</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94430</t>
+          <t>94236</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56616</t>
+          <t>54616</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87394</t>
+          <t>88634</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69590</t>
+          <t>68841</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104377</t>
+          <t>102202</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145467</t>
+          <t>145662</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159319</t>
+          <t>159580</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197227</t>
+          <t>198096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124461</t>
+          <t>124649</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>155688</t>
+          <t>156799</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>295273</t>
+          <t>293506</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>343009</t>
+          <t>344276</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27308</t>
+          <t>28268</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53528</t>
+          <t>52690</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>19654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41410</t>
+          <t>39789</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53014</t>
+          <t>53734</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84257</t>
+          <t>85793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45212</t>
+          <t>44040</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77049</t>
+          <t>76011</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31723</t>
+          <t>31982</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59498</t>
+          <t>59982</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84527</t>
+          <t>83000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128660</t>
+          <t>125916</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>227119</t>
+          <t>228379</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>288714</t>
+          <t>284199</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>181231</t>
+          <t>179428</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>232342</t>
+          <t>231133</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>421616</t>
+          <t>422398</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>501733</t>
+          <t>498450</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>321232</t>
+          <t>317110</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>386459</t>
+          <t>384984</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>198059</t>
+          <t>193457</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>250288</t>
+          <t>248944</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>534659</t>
+          <t>533166</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>617599</t>
+          <t>621646</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>671408</t>
+          <t>672158</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>746722</t>
+          <t>748468</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>410876</t>
+          <t>413225</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>475399</t>
+          <t>475704</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1108845</t>
+          <t>1104026</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1203796</t>
+          <t>1207115</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24833</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22261</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32461</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50126</t>
+          <t>51181</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>24051</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43806</t>
+          <t>42630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68759</t>
+          <t>68236</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>44963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30391</t>
+          <t>30493</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44046</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69512</t>
+          <t>70089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36193</t>
+          <t>35818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58801</t>
+          <t>59277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>27355</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53620</t>
+          <t>53979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80144</t>
+          <t>79980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24121</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49375</t>
+          <t>49321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22780</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46258</t>
+          <t>45749</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53208</t>
+          <t>53705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89506</t>
+          <t>86833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42043</t>
+          <t>43374</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73866</t>
+          <t>75161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>33561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58368</t>
+          <t>60262</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82490</t>
+          <t>83281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123352</t>
+          <t>122017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>189424</t>
+          <t>190981</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>242360</t>
+          <t>243373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146897</t>
+          <t>148445</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>192928</t>
+          <t>192708</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>351745</t>
+          <t>350847</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>419730</t>
+          <t>420124</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>249733</t>
+          <t>246630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>304424</t>
+          <t>301412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155891</t>
+          <t>157792</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202871</t>
+          <t>201591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>423608</t>
+          <t>419385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>494173</t>
+          <t>493859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315179</t>
+          <t>311584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373583</t>
+          <t>371725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202949</t>
+          <t>200154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246372</t>
+          <t>247413</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>531479</t>
+          <t>528666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>607853</t>
+          <t>607242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>17724</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25036</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19839</t>
+          <t>19849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20599</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47773</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79045</t>
+          <t>78938</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>42648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69002</t>
+          <t>70376</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>96342</t>
+          <t>96936</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137978</t>
+          <t>140010</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67291</t>
+          <t>69483</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101372</t>
+          <t>100997</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55594</t>
+          <t>55581</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82175</t>
+          <t>84385</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129806</t>
+          <t>131490</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175999</t>
+          <t>174046</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169479</t>
+          <t>169313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207333</t>
+          <t>206596</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>146387</t>
+          <t>146404</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>180327</t>
+          <t>180205</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>322068</t>
+          <t>327577</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>375183</t>
+          <t>377351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35313</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66964</t>
+          <t>64539</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36345</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61989</t>
+          <t>62750</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76123</t>
+          <t>80798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117173</t>
+          <t>119478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64838</t>
+          <t>66664</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103626</t>
+          <t>100825</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50986</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82180</t>
+          <t>84563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>128175</t>
+          <t>126859</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>172962</t>
+          <t>174474</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>284236</t>
+          <t>280238</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>349113</t>
+          <t>350188</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>213989</t>
+          <t>217127</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>269888</t>
+          <t>270392</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>518632</t>
+          <t>517165</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>605349</t>
+          <t>601592</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>361149</t>
+          <t>357008</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>427989</t>
+          <t>429364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>242165</t>
+          <t>241471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>296516</t>
+          <t>298693</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>617771</t>
+          <t>618990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>707492</t>
+          <t>708491</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>534810</t>
+          <t>537972</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>612805</t>
+          <t>616550</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>374819</t>
+          <t>376423</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>436617</t>
+          <t>442339</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>932968</t>
+          <t>931401</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1034394</t>
+          <t>1030663</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
